--- a/output/pdf_financials_xlsx/DIGI.xlsx
+++ b/output/pdf_financials_xlsx/DIGI.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.594325</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.276224</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.58862</v>
       </c>
     </row>
     <row r="93">
@@ -3221,7 +3221,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3541,7 +3545,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.594325</v>
       </c>

--- a/output/pdf_financials_xlsx/DIGI.xlsx
+++ b/output/pdf_financials_xlsx/DIGI.xlsx
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004202</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.014242</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.01703</v>
       </c>
     </row>
     <row r="35">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.004202</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.637028</v>
+        <v>1.65127</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.01703</v>
       </c>
     </row>
     <row r="37">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.016217</v>
+        <v>0.012015</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.105608</v>
+        <v>0.091366</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.558115</v>
+        <v>3.541085</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/DIGI.xlsx
+++ b/output/pdf_financials_xlsx/DIGI.xlsx
@@ -2073,7 +2073,7 @@
         <v>0.024188</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.04925</v>
+        <v>-0.055368</v>
       </c>
     </row>
     <row r="102">
@@ -2153,7 +2153,7 @@
         <v>-0.204248</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.189223</v>
+        <v>0.084605</v>
       </c>
     </row>
     <row r="107">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.014324</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.013702</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.008697</v>
       </c>
     </row>
     <row r="116">
@@ -3609,7 +3609,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.014324</v>
       </c>
@@ -3913,7 +3917,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -4252,7 +4260,11 @@
           <t>Proceeds from sale of Investments</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
